--- a/LAB2/Таблица_60_тактов.xlsx
+++ b/LAB2/Таблица_60_тактов.xlsx
@@ -5252,7 +5252,7 @@
         <v>0</v>
       </c>
       <c r="AA56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" ht="17.25">
@@ -5332,10 +5332,10 @@
         <v>0</v>
       </c>
       <c r="Z57" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" ht="17.25">
@@ -5412,10 +5412,10 @@
         <v>0</v>
       </c>
       <c r="Y58" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z58" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="1">
         <v>0</v>
@@ -5492,10 +5492,10 @@
         <v>0</v>
       </c>
       <c r="X59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y59" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z59" s="4">
         <v>0</v>
@@ -5572,10 +5572,10 @@
         <v>0</v>
       </c>
       <c r="W60" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X60" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y60" s="4">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>1</v>
       </c>
       <c r="AA61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
